--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15460,7 +15478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15504,6 +15522,172 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1980_81_0424 'TJ Slezan Frýdek-Místek' prev→CLUB_S1979_80_0436 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0363 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0364 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0365 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0366 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0367 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0368 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0370 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0371 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0372 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1980_81_0373 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0016</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1980_81_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0017</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1980_81_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -47366,6 +47550,347 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0424</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0424 'TJ Slezan Frýdek-Místek' prev→CLUB_S1979_80_0436 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0363</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0363 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0364</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0364 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0365</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0365 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0366</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0366 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0367</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0367 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0368</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0368 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0370</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0370 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0371</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0371 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0372</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0372 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0373</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0373 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0016</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1980_81_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0017</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1980_81_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15478,7 +15478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15528,7 +15528,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1980_81_0424 'TJ Slezan Frýdek-Místek' prev→CLUB_S1979_80_0436 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15540,7 +15540,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0363 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15552,7 +15552,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0364 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15564,7 +15564,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0365 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15576,7 +15576,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0366 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15588,7 +15588,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0367 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15600,7 +15600,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0368 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15612,7 +15612,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0370 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15624,7 +15624,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0371 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15636,7 +15636,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0372 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15648,7 +15648,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1980_81_0373 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15658,14 +15658,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S1980_81_0016</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1980_81_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15675,17 +15670,468 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S1980_81_0017</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1980_81_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21290,12 +21736,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -21757,12 +22203,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -22098,12 +22544,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -22491,12 +22937,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -22533,12 +22979,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -22617,12 +23063,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22701,12 +23147,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -22743,12 +23189,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -22911,12 +23357,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -23126,12 +23572,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -23168,12 +23614,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -23336,12 +23782,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -23462,12 +23908,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23704,12 +24150,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bratislava = TJ Slávia Ekonom Bratislava (Wiki D42 - registr ustavy 04/2026). Slovensky/Bratislavsky kraj. **Ekonom** = Vysoká škola ekonomická (EU Bratislava). Patterns: Slávia Ekonom -&gt; Slávia Ekonóm. city Bratislava.</t>
+          <t>Bratislava = TJ Slávia Ekonom Bratislava (Wiki D42 - registr ustavy 04/2026). Slovensky/Bratislavsky kraj. **Ekonom** = Vysoká škola ekonomická (EU Bratislava). Patterns: Slávia Ekonom -&gt; Slávia Ekonóm. city Bratislava. || TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Slávia Ekonom Bratislava</t>
+          <t>Bratislava</t>
         </is>
       </c>
     </row>
@@ -23746,12 +24192,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -24082,12 +24528,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov).</t>
+          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov). || TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Rudá Hvězda Žižkov</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -24198,12 +24644,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Praha = TJ UDPM JF Praha (Wiki D42 - registr ustavy 04/2026). **UDPM** = Ústřední dům pionýrů a mládeže, **JF** = Julia Fučíka (pojmenovani). Studentsky/mladez klub. city Praha.</t>
+          <t>Praha = TJ UDPM JF Praha (Wiki D42 - registr ustavy 04/2026). **UDPM** = Ústřední dům pionýrů a mládeže, **JF** = Julia Fučíka (pojmenovani). Studentsky/mladez klub. city Praha. || TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UDPM JF Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -24282,12 +24728,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Plzeň-Černice = TJ Sokol Černice (Wiki D42 - registr ustavy 04/2026). Plzensky/Zapadocesky kraj. Mestska cast Plzně. city Plzeň (Černice).</t>
+          <t>Plzeň-Černice = TJ Sokol Černice (Wiki D42 - registr ustavy 04/2026). Plzensky/Zapadocesky kraj. Mestska cast Plzně. city Plzeň (Černice). || TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Černice</t>
+          <t>Horní Počernice</t>
         </is>
       </c>
     </row>
@@ -25179,12 +25625,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -27310,12 +27756,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -27651,12 +28097,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -27824,12 +28270,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -28279,12 +28725,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -28571,12 +29017,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28665,12 +29111,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30945,12 +31391,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb.</t>
+          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb. || TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Lokomotiva depo Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -31227,12 +31673,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -31489,12 +31935,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -32374,12 +32820,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -32421,12 +32867,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -33158,12 +33604,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -33588,12 +34034,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -34557,12 +35003,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -35450,12 +35896,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice.</t>
+          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice. || TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Povodí Labe Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -35591,12 +36037,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice.</t>
+          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice. || TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>SSM SNV Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -35989,12 +36435,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice.</t>
+          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice. || TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Dopravní podnik Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -37089,12 +37535,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -39215,12 +39661,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -39682,12 +40128,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -40327,12 +40773,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá.</t>
+          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá. || TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Důl Prezident Gottwald Horní Suchá</t>
+          <t>Horní Suchá</t>
         </is>
       </c>
     </row>
@@ -40893,12 +41339,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá.</t>
+          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá. || TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Důl Prezident Gottwald Horní Suchá</t>
+          <t>Horní Suchá</t>
         </is>
       </c>
     </row>
@@ -47556,11 +48002,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -47605,21 +48051,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0424</t>
+          <t>CLUB_S1980_81_0002</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0424 'TJ Slezan Frýdek-Místek' prev→CLUB_S1979_80_0436 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -47627,21 +48071,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0363</t>
+          <t>CLUB_S1980_81_0013</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0363 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -47649,21 +48091,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0364</t>
+          <t>CLUB_S1980_81_0021</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0364 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -47671,21 +48111,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0365</t>
+          <t>CLUB_S1980_81_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0365 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -47693,21 +48131,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0366</t>
+          <t>CLUB_S1980_81_0031</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0366 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -47715,21 +48151,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0367</t>
+          <t>CLUB_S1980_81_0033</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0367 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -47737,21 +48171,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0368</t>
+          <t>CLUB_S1980_81_0035</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0368 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -47759,21 +48191,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0370</t>
+          <t>CLUB_S1980_81_0036</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0370 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -47781,21 +48211,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0371</t>
+          <t>CLUB_S1980_81_0040</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0371 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -47803,21 +48231,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0372</t>
+          <t>CLUB_S1980_81_0045</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0372 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -47825,21 +48251,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0373</t>
+          <t>CLUB_S1980_81_0046</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0373 fate nekonzist. ['reorganizace', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -47847,21 +48271,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NODE_S1980_81_0016</t>
+          <t>CLUB_S1980_81_0050</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1980_81_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -47869,24 +48291,782 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NODE_S1980_81_0017</t>
+          <t>CLUB_S1980_81_0053</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1980_81_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1980_81_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0059</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0061</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0069</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0069</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0072</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0074</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0096</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0145</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0153</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0157</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0157</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0167</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0173</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0175</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0186</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0225</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0231</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0235</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0238</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0258</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0259</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0266</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0275</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0280</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0286</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0287</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0303</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0308</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0327</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0330</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0339</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0365</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0406</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0415</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0424</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0426</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0441</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0454</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15478,7 +15478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15528,7 +15528,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15540,7 +15540,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15552,7 +15552,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15564,7 +15564,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15576,7 +15576,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15588,7 +15588,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15600,7 +15600,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15612,7 +15612,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15624,7 +15624,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15636,7 +15636,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15648,7 +15648,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15660,7 +15660,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15672,7 +15672,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15684,7 +15684,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15696,7 +15696,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15708,7 +15708,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15720,7 +15720,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15732,7 +15732,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15744,7 +15744,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15756,7 +15756,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15780,7 +15780,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15792,7 +15792,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15804,7 +15804,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15816,7 +15816,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15828,7 +15828,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15840,7 +15840,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15852,7 +15852,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15864,7 +15864,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15876,7 +15876,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15888,7 +15888,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15900,7 +15900,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15924,7 +15924,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15936,7 +15936,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15948,7 +15948,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -15960,7 +15960,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -15972,7 +15972,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -15984,7 +15984,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -15996,7 +15996,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16008,7 +16008,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16020,118 +16020,10 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16148,7 +16040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16207,6 +16099,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16249,6 +16146,11 @@
           <t>12 týmů, jeden stůl. Mistr: TJ Vítkovice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16296,6 +16198,11 @@
           <t>Série Poprad – Zetor Brno 2:3. 1. a 3. utkání doma; 5. utkání na neutrálním ledě v Ostravě. Při remíze 3x 5 min + nájezdy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16338,6 +16245,11 @@
           <t>I.ČNHL (2 skupiny po 12 → finálová skupina + 2× o udržení) + SNHL (12).</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16380,6 +16292,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16422,6 +16339,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16464,6 +16386,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16506,6 +16433,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16548,6 +16480,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16590,6 +16527,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16637,6 +16579,11 @@
           <t>Utkání Karviná – Opava bylo oboustranně kontumováno 0:5; nikomu nebyly přičteny body a oběma bylo přičteno skóre 0:5.</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16862,6 +16809,11 @@
           <t>2 skupiny po 4 týmech.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0012</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16904,6 +16856,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0013</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16946,6 +16903,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0014</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16993,6 +16955,11 @@
           <t>Kvalifikace se hrála jednokolově v Martině.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0015</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17035,6 +17002,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0016</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17077,6 +17049,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17119,6 +17096,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0017</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17161,6 +17143,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0019</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17203,6 +17190,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17287,6 +17279,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17329,6 +17326,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17455,6 +17457,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0024</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17586,6 +17593,11 @@
           <t>kvalifikace o KP I.třídy</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0028</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17633,6 +17645,11 @@
           <t>Kvalifikace o II.třídu</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0029</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17843,6 +17860,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17885,6 +17907,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0034</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17927,6 +17954,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0035</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17969,6 +18001,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0036</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18011,6 +18048,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0037</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18095,6 +18137,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0039</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18142,6 +18189,11 @@
           <t>kvalifikace o II.třídu</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -18184,6 +18236,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -18226,6 +18283,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -18268,6 +18330,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -18310,6 +18377,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -18352,6 +18424,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18399,6 +18476,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -18441,6 +18523,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18483,6 +18570,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18525,6 +18617,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0055</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18567,6 +18664,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0056</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18609,6 +18711,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0057</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18651,6 +18758,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0058</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18735,6 +18847,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0060</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18777,6 +18894,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0064</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18819,6 +18941,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0065</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18987,6 +19114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0066</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -19029,6 +19161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0067</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19076,6 +19213,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0068</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -19118,6 +19260,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0069</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19160,6 +19307,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0070</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -19748,6 +19900,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0081</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19790,6 +19947,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0082</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19874,6 +20036,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0084</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19958,6 +20125,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0085</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20173,6 +20345,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0092</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -20215,6 +20392,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0093</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -20257,6 +20439,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0097</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -20297,6 +20484,11 @@
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0098</t>
         </is>
       </c>
     </row>
@@ -21736,12 +21928,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -22979,12 +23171,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -23063,12 +23255,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23147,12 +23339,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23357,12 +23549,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -28270,12 +28462,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -35003,12 +35195,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -37535,12 +37727,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -40128,12 +40320,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -48002,7 +48194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48056,12 +48248,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0002</t>
+          <t>CLUB_S1980_81_0013</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48076,12 +48268,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0013</t>
+          <t>CLUB_S1980_81_0021</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48096,12 +48288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0021</t>
+          <t>CLUB_S1980_81_0030</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48116,12 +48308,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0030</t>
+          <t>CLUB_S1980_81_0036</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48136,12 +48328,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0031</t>
+          <t>CLUB_S1980_81_0045</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48156,12 +48348,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0033</t>
+          <t>CLUB_S1980_81_0046</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48176,12 +48368,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0035</t>
+          <t>CLUB_S1980_81_0050</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48196,12 +48388,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0036</t>
+          <t>CLUB_S1980_81_0053</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48216,12 +48408,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0040</t>
+          <t>CLUB_S1980_81_0059</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48236,12 +48428,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0045</t>
+          <t>CLUB_S1980_81_0061</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48256,12 +48448,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0046</t>
+          <t>CLUB_S1980_81_0069</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48276,12 +48468,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0050</t>
+          <t>CLUB_S1980_81_0069</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48296,12 +48488,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0053</t>
+          <t>CLUB_S1980_81_0072</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48316,12 +48508,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0059</t>
+          <t>CLUB_S1980_81_0074</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48336,12 +48528,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0061</t>
+          <t>CLUB_S1980_81_0096</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48356,12 +48548,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0069</t>
+          <t>CLUB_S1980_81_0145</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48376,12 +48568,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0069</t>
+          <t>CLUB_S1980_81_0153</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48396,12 +48588,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0072</t>
+          <t>CLUB_S1980_81_0157</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48416,12 +48608,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0074</t>
+          <t>CLUB_S1980_81_0167</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48436,12 +48628,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0096</t>
+          <t>CLUB_S1980_81_0173</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48456,7 +48648,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0145</t>
+          <t>CLUB_S1980_81_0175</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -48476,12 +48668,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0153</t>
+          <t>CLUB_S1980_81_0186</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -48496,12 +48688,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0157</t>
+          <t>CLUB_S1980_81_0225</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48516,12 +48708,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0157</t>
+          <t>CLUB_S1980_81_0231</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48536,12 +48728,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0167</t>
+          <t>CLUB_S1980_81_0235</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48556,12 +48748,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0173</t>
+          <t>CLUB_S1980_81_0238</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48576,12 +48768,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0175</t>
+          <t>CLUB_S1980_81_0258</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48596,12 +48788,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0186</t>
+          <t>CLUB_S1980_81_0259</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48616,12 +48808,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0225</t>
+          <t>CLUB_S1980_81_0266</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48636,12 +48828,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0231</t>
+          <t>CLUB_S1980_81_0275</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48656,12 +48848,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0235</t>
+          <t>CLUB_S1980_81_0280</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48676,12 +48868,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0238</t>
+          <t>CLUB_S1980_81_0286</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48696,12 +48888,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0258</t>
+          <t>CLUB_S1980_81_0287</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48716,12 +48908,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0259</t>
+          <t>CLUB_S1980_81_0303</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48736,12 +48928,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0266</t>
+          <t>CLUB_S1980_81_0327</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48756,12 +48948,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0275</t>
+          <t>CLUB_S1980_81_0330</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48776,12 +48968,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0280</t>
+          <t>CLUB_S1980_81_0339</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48796,12 +48988,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0286</t>
+          <t>CLUB_S1980_81_0406</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48816,12 +49008,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0287</t>
+          <t>CLUB_S1980_81_0415</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48836,12 +49028,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0303</t>
+          <t>CLUB_S1980_81_0424</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48856,12 +49048,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0308</t>
+          <t>CLUB_S1980_81_0441</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48876,197 +49068,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0327</t>
+          <t>CLUB_S1980_81_0454</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0330</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0339</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0365</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0406</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0415</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0424</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0426</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0441</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1980_81_0454</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15478,7 +15478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15526,33 +15526,43 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] ČSAD Tábor — odstoupil (club_id: CLUB_S1980_81_0055)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Start VD Luby — odstoupily (club_id: CLUB_S1980_81_0231)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15564,7 +15574,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15576,7 +15586,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15588,7 +15598,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15600,7 +15610,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15612,7 +15622,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15624,7 +15634,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15636,7 +15646,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15648,7 +15658,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'ČSAD Tábor — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15660,7 +15670,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15672,7 +15682,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15684,7 +15694,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15696,7 +15706,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15708,7 +15718,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15720,7 +15730,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15732,7 +15742,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15744,7 +15754,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15756,7 +15766,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15768,7 +15778,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15780,7 +15790,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15792,7 +15802,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15804,7 +15814,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15816,7 +15826,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15828,7 +15838,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15840,7 +15850,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15852,7 +15862,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'Start VD Luby — odstoupily' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15876,7 +15886,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15888,7 +15898,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15900,7 +15910,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15912,7 +15922,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15924,7 +15934,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15936,7 +15946,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15948,7 +15958,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -15960,7 +15970,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -15972,7 +15982,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -15984,7 +15994,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -15996,7 +16006,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16008,7 +16018,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16020,10 +16030,58 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24179,7 +24237,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor.</t>
+          <t>DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor. || TBD: extrahováno z block_name: 'ČSAD Tábor — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -31865,7 +31923,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach] || TBD: extrahováno z block_name: 'Start VD Luby — odstoupily' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -48194,7 +48252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48408,12 +48466,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0059</t>
+          <t>CLUB_S1980_81_0055</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: extrahováno z block_name: 'ČSAD Tábor — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -48428,12 +48486,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0061</t>
+          <t>CLUB_S1980_81_0059</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48448,12 +48506,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0069</t>
+          <t>CLUB_S1980_81_0061</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48473,7 +48531,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48488,12 +48546,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0072</t>
+          <t>CLUB_S1980_81_0069</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48508,12 +48566,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0074</t>
+          <t>CLUB_S1980_81_0072</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48528,12 +48586,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0096</t>
+          <t>CLUB_S1980_81_0074</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48548,12 +48606,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0145</t>
+          <t>CLUB_S1980_81_0096</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48568,12 +48626,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0153</t>
+          <t>CLUB_S1980_81_0145</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48588,12 +48646,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0157</t>
+          <t>CLUB_S1980_81_0153</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48608,12 +48666,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0167</t>
+          <t>CLUB_S1980_81_0157</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48628,12 +48686,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0173</t>
+          <t>CLUB_S1980_81_0167</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48648,7 +48706,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0175</t>
+          <t>CLUB_S1980_81_0173</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -48668,12 +48726,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0186</t>
+          <t>CLUB_S1980_81_0175</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48688,12 +48746,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0225</t>
+          <t>CLUB_S1980_81_0186</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -48708,12 +48766,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0231</t>
+          <t>CLUB_S1980_81_0225</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48728,12 +48786,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0235</t>
+          <t>CLUB_S1980_81_0231</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48748,12 +48806,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0238</t>
+          <t>CLUB_S1980_81_0231</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: extrahováno z block_name: 'Start VD Luby — odstoupily' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -48768,12 +48826,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0258</t>
+          <t>CLUB_S1980_81_0235</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48788,12 +48846,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0259</t>
+          <t>CLUB_S1980_81_0238</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48808,12 +48866,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0266</t>
+          <t>CLUB_S1980_81_0258</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48828,12 +48886,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0275</t>
+          <t>CLUB_S1980_81_0259</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48848,12 +48906,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0280</t>
+          <t>CLUB_S1980_81_0266</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48868,12 +48926,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0286</t>
+          <t>CLUB_S1980_81_0275</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48888,7 +48946,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0287</t>
+          <t>CLUB_S1980_81_0280</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -48908,12 +48966,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0303</t>
+          <t>CLUB_S1980_81_0286</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48928,12 +48986,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0327</t>
+          <t>CLUB_S1980_81_0287</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48948,12 +49006,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0330</t>
+          <t>CLUB_S1980_81_0303</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48968,12 +49026,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0339</t>
+          <t>CLUB_S1980_81_0327</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48988,12 +49046,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0406</t>
+          <t>CLUB_S1980_81_0330</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49008,12 +49066,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0415</t>
+          <t>CLUB_S1980_81_0339</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49028,12 +49086,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0424</t>
+          <t>CLUB_S1980_81_0406</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -49048,12 +49106,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1980_81_0441</t>
+          <t>CLUB_S1980_81_0415</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49068,17 +49126,57 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>CLUB_S1980_81_0424</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1980_81_0441</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>CLUB_S1980_81_0454</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -57856,7 +57954,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / základní část / ČSAD Tábor — odstoupil</t>
+          <t>Krajský přebor / základní část</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -62143,7 +62241,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / Start VD Luby — odstoupily</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15478,7 +15478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16082,6 +16082,126 @@
         </is>
       </c>
       <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -48252,7 +48372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49175,8 +49295,208 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TJ Motor České Budějovice</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TJ Poldi SONP Kladno</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TJ Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TJ CHZ Litvínov</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TJ Dukla Trenčín</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TJ Tesla Pardubice</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TJ Sparta ČKD Praha</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TJ VSŽ Košice</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TJ Gottwaldov</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TJ Škoda Plzeň</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F45"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -718,29 +718,27 @@
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L4" t="n">
+        <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -806,29 +804,27 @@
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L5" t="n">
+        <v>119</v>
       </c>
       <c r="M5" t="n">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -894,29 +890,27 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L6" t="n">
+        <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -982,29 +976,27 @@
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L7" t="n">
+        <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1070,29 +1062,27 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>19</v>
       </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L8" t="n">
+        <v>173</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1158,29 +1148,27 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L9" t="n">
+        <v>181</v>
       </c>
       <c r="M9" t="n">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1246,29 +1234,27 @@
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L10" t="n">
+        <v>190</v>
       </c>
       <c r="M10" t="n">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1334,29 +1320,27 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J11" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L11" t="n">
+        <v>178</v>
       </c>
       <c r="M11" t="n">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1428,23 +1412,21 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L12" t="n">
+        <v>199</v>
       </c>
       <c r="M12" t="n">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1521,23 +1503,21 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L13" t="n">
+        <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1603,29 +1583,27 @@
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L14" t="n">
+        <v>172</v>
       </c>
       <c r="M14" t="n">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1697,23 +1675,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L15" t="n">
+        <v>198</v>
       </c>
       <c r="M15" t="n">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -15478,7 +15454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16082,126 +16058,6 @@
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -48372,7 +48228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49295,208 +49151,8 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>TJ Motor České Budějovice</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TJ Poldi SONP Kladno</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>TJ Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>TJ CHZ Litvínov</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>TJ Dukla Trenčín</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>TJ Tesla Pardubice</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>TJ Sparta ČKD Praha</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TJ VSŽ Košice</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>TJ Gottwaldov</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TJ Škoda Plzeň</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -45435,10 +45435,10 @@
         <v>22</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
         <v>165</v>
@@ -46333,7 +46333,7 @@
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
         <v>135</v>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -16074,7 +16074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16136,6 +16136,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -16420,6 +16420,16 @@
           <t>NODE_S1980_81_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16434,6 +16444,14 @@
         <is>
           <t>NODE_S1979_80_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16467,6 +16485,8 @@
           <t>NODE_S1980_81_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16481,6 +16501,14 @@
         <is>
           <t>NODE_S1979_80_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -16514,6 +16542,8 @@
           <t>NODE_S1980_81_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16528,6 +16558,14 @@
         <is>
           <t>NODE_S1979_80_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16707,6 +16745,8 @@
           <t>NODE_S1980_81_0004</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16716,6 +16756,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-1.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16749,6 +16797,8 @@
           <t>NODE_S1980_81_0004</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16758,6 +16808,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-1.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -16791,6 +16849,12 @@
           <t>NODE_S1980_81_0005</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0012</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16805,6 +16869,14 @@
         <is>
           <t>ASVŠ Dukla Trenčín B hrála domácí utkání v Topoľčanech.</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -17177,6 +17249,8 @@
           <t>NODE_S1980_81_0019</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17191,6 +17265,14 @@
         <is>
           <t>NODE_S1979_80_0019</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -17271,6 +17353,8 @@
           <t>NODE_S1980_81_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17280,6 +17364,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -17407,6 +17499,12 @@
           <t>NODE_S1980_81_0025</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0028</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17416,6 +17514,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -17449,6 +17555,8 @@
           <t>NODE_S1980_81_0025</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17458,6 +17566,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -17810,6 +17926,8 @@
           <t>NODE_S1980_81_0025</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17819,6 +17937,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -18035,6 +18161,8 @@
           <t>NODE_S1980_81_0039</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18049,6 +18177,14 @@
         <is>
           <t>NODE_S1979_80_0036</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -18129,6 +18265,8 @@
           <t>NODE_S1980_81_0039</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18138,6 +18276,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -18651,6 +18797,8 @@
           <t>NODE_S1980_81_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18665,6 +18813,14 @@
         <is>
           <t>NODE_S1979_80_0055</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -18839,6 +18995,8 @@
           <t>NODE_S1980_81_0052</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18848,6 +19006,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -19022,6 +19188,16 @@
           <t>NODE_S1980_81_0060</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0063</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0064</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19031,6 +19207,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -19064,6 +19248,8 @@
           <t>NODE_S1980_81_0060</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19073,6 +19259,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -19106,6 +19300,8 @@
           <t>NODE_S1980_81_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19115,6 +19311,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>6.–9. ZČ</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -19556,6 +19760,8 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19565,6 +19771,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -19766,6 +19980,8 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19775,6 +19991,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -19808,6 +20032,8 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19817,6 +20043,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -19850,6 +20084,8 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19859,6 +20095,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -19892,6 +20136,8 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19901,6 +20147,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -20028,6 +20282,12 @@
           <t>NODE_S1980_81_0083</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0092</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20037,6 +20297,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -20117,6 +20385,8 @@
           <t>NODE_S1980_81_0083</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20126,6 +20396,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -20337,6 +20615,8 @@
           <t>NODE_S1980_81_0083</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20346,6 +20626,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -20651,6 +20939,8 @@
           <t>NODE_S1980_81_0096</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20660,6 +20950,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -714,6 +714,11 @@
           <t>TJ Vítkovice</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -16485,8 +16490,6 @@
           <t>NODE_S1980_81_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16542,8 +16545,6 @@
           <t>NODE_S1980_81_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16745,8 +16746,6 @@
           <t>NODE_S1980_81_0004</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16797,8 +16796,6 @@
           <t>NODE_S1980_81_0004</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16849,7 +16846,6 @@
           <t>NODE_S1980_81_0005</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>NODE_S1980_81_0012</t>
@@ -17249,8 +17245,6 @@
           <t>NODE_S1980_81_0019</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17353,8 +17347,6 @@
           <t>NODE_S1980_81_0019</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17504,7 +17496,6 @@
           <t>NODE_S1980_81_0028</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17555,8 +17546,6 @@
           <t>NODE_S1980_81_0025</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17926,8 +17915,6 @@
           <t>NODE_S1980_81_0025</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18161,8 +18148,6 @@
           <t>NODE_S1980_81_0039</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18265,8 +18250,6 @@
           <t>NODE_S1980_81_0039</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18797,8 +18780,6 @@
           <t>NODE_S1980_81_0052</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18995,8 +18976,6 @@
           <t>NODE_S1980_81_0052</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19248,8 +19227,6 @@
           <t>NODE_S1980_81_0060</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19300,8 +19277,6 @@
           <t>NODE_S1980_81_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19760,8 +19735,6 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19980,8 +19953,6 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20032,8 +20003,6 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20084,8 +20053,6 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20136,8 +20103,6 @@
           <t>NODE_S1980_81_0068</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20287,7 +20252,6 @@
           <t>NODE_S1980_81_0092</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20385,8 +20349,6 @@
           <t>NODE_S1980_81_0083</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20615,8 +20577,6 @@
           <t>NODE_S1980_81_0083</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20939,8 +20899,6 @@
           <t>NODE_S1980_81_0096</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -43261,7 +43219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43357,6 +43315,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>opraveno dle auditu v rozsahu kritických a hlavních vysokých vad</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TJ Vítkovice</t>
         </is>
       </c>
     </row>

--- a/data/S1980_81_FINAL.xlsx
+++ b/data/S1980_81_FINAL.xlsx
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +89,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -98,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +119,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -56738,7 +56749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56795,7 +56806,7 @@
           <t>CLUB_S1980_81_0013</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56815,7 +56826,7 @@
           <t>CLUB_S1980_81_0021</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56835,7 +56846,7 @@
           <t>CLUB_S1980_81_0030</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56855,7 +56866,7 @@
           <t>CLUB_S1980_81_0036</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56875,7 +56886,7 @@
           <t>CLUB_S1980_81_0045</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56895,7 +56906,7 @@
           <t>CLUB_S1980_81_0046</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56915,7 +56926,7 @@
           <t>CLUB_S1980_81_0050</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56935,7 +56946,7 @@
           <t>CLUB_S1980_81_0053</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56955,7 +56966,7 @@
           <t>CLUB_S1980_81_0055</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'ČSAD Tábor — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
@@ -56975,7 +56986,7 @@
           <t>CLUB_S1980_81_0059</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Slávia Ekonom Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56995,7 +57006,7 @@
           <t>CLUB_S1980_81_0061</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57015,7 +57026,7 @@
           <t>CLUB_S1980_81_0069</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57035,7 +57046,7 @@
           <t>CLUB_S1980_81_0069</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -57055,7 +57066,7 @@
           <t>CLUB_S1980_81_0072</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57075,7 +57086,7 @@
           <t>CLUB_S1980_81_0074</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -57095,7 +57106,7 @@
           <t>CLUB_S1980_81_0096</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57115,7 +57126,7 @@
           <t>CLUB_S1980_81_0145</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57135,7 +57146,7 @@
           <t>CLUB_S1980_81_0153</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -57155,7 +57166,7 @@
           <t>CLUB_S1980_81_0157</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57175,7 +57186,7 @@
           <t>CLUB_S1980_81_0167</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57195,7 +57206,7 @@
           <t>CLUB_S1980_81_0173</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57215,7 +57226,7 @@
           <t>CLUB_S1980_81_0175</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57235,7 +57246,7 @@
           <t>CLUB_S1980_81_0186</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
@@ -57255,7 +57266,7 @@
           <t>CLUB_S1980_81_0225</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57275,7 +57286,7 @@
           <t>CLUB_S1980_81_0231</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57295,7 +57306,7 @@
           <t>CLUB_S1980_81_0231</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'Start VD Luby — odstoupily' [fix_club_notes_in_block_name]</t>
         </is>
@@ -57315,7 +57326,7 @@
           <t>CLUB_S1980_81_0235</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -57335,7 +57346,7 @@
           <t>CLUB_S1980_81_0238</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57355,7 +57366,7 @@
           <t>CLUB_S1980_81_0258</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57375,7 +57386,7 @@
           <t>CLUB_S1980_81_0259</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57395,7 +57406,7 @@
           <t>CLUB_S1980_81_0266</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -57415,7 +57426,7 @@
           <t>CLUB_S1980_81_0275</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57435,7 +57446,7 @@
           <t>CLUB_S1980_81_0280</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -57455,7 +57466,7 @@
           <t>CLUB_S1980_81_0286</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57475,7 +57486,7 @@
           <t>CLUB_S1980_81_0287</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -57495,7 +57506,7 @@
           <t>CLUB_S1980_81_0303</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -57515,7 +57526,7 @@
           <t>CLUB_S1980_81_0327</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57535,7 +57546,7 @@
           <t>CLUB_S1980_81_0330</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57555,7 +57566,7 @@
           <t>CLUB_S1980_81_0339</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57575,7 +57586,7 @@
           <t>CLUB_S1980_81_0406</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -57595,7 +57606,7 @@
           <t>CLUB_S1980_81_0415</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57615,7 +57626,7 @@
           <t>CLUB_S1980_81_0424</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1979_80_0436 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57635,7 +57646,7 @@
           <t>CLUB_S1980_81_0441</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57655,11 +57666,37 @@
           <t>CLUB_S1980_81_0454</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>30_Středočeský kvalifikace o KP I.třídy (Středočeský kraj) · NODE_S1980_81_0032</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Sokol Pátek nevyužil možnost postupu a hokej tam skončil.), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F45"/>
